--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755521587_h_4.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755521587_h_4.xlsx
@@ -658,7 +658,7 @@
         <v>0.01785786076801291</v>
       </c>
       <c r="C2" t="n">
-        <v>24851088</v>
+        <v>6212772</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>24851088</v>
+        <v>6212772</v>
       </c>
       <c r="K2" t="n">
-        <v>18509729</v>
+        <v>4358443</v>
       </c>
       <c r="L2" t="n">
-        <v>11320880</v>
+        <v>2492260</v>
       </c>
       <c r="M2" t="n">
-        <v>3052645</v>
+        <v>632371</v>
       </c>
       <c r="N2" t="n">
-        <v>196318</v>
+        <v>33260</v>
       </c>
       <c r="O2" t="n">
-        <v>1769663</v>
+        <v>384196</v>
       </c>
       <c r="P2" t="n">
-        <v>700325</v>
+        <v>158474</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999725818634033</v>
+        <v>0.9999396204948425</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9399536848068237</v>
+        <v>0.8852847814559937</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8772578239440918</v>
+        <v>0.7724735736846924</v>
       </c>
       <c r="T2" t="n">
-        <v>0.817011296749115</v>
+        <v>0.6771698594093323</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6801459193229675</v>
+        <v>0.4627220630645752</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8699347376823425</v>
+        <v>0.7555758953094482</v>
       </c>
       <c r="W2" t="n">
-        <v>0.905321478843689</v>
+        <v>0.8189786076545715</v>
       </c>
       <c r="X2" t="n">
-        <v>24851088</v>
+        <v>6212772</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>24851088</v>
+        <v>6212772</v>
       </c>
       <c r="AF2" t="n">
-        <v>17857588</v>
+        <v>4226955</v>
       </c>
       <c r="AG2" t="n">
-        <v>10387905</v>
+        <v>2305814</v>
       </c>
       <c r="AH2" t="n">
-        <v>2705736</v>
+        <v>572610</v>
       </c>
       <c r="AI2" t="n">
-        <v>170728</v>
+        <v>30514</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1614925</v>
+        <v>353874</v>
       </c>
       <c r="AK2" t="n">
-        <v>656266</v>
+        <v>148866</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9041380882263184</v>
+        <v>0.8560509085655212</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.8105198740959167</v>
+        <v>0.7196477651596069</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.7304050922393799</v>
+        <v>0.6182972192764282</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.4829482436180115</v>
+        <v>0.3452669084072113</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.7946620583534241</v>
+        <v>0.6965283155441284</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.848928689956665</v>
+        <v>0.7702767848968506</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.004485712249273131</v>
       </c>
       <c r="C3" t="n">
-        <v>133</v>
+        <v>89</v>
       </c>
       <c r="D3" t="n">
-        <v>18509729</v>
+        <v>4358443</v>
       </c>
       <c r="E3" t="n">
-        <v>1102725</v>
+        <v>516605</v>
       </c>
       <c r="F3" t="n">
-        <v>53777</v>
+        <v>25340</v>
       </c>
       <c r="G3" t="n">
-        <v>11392</v>
+        <v>4994</v>
       </c>
       <c r="H3" t="n">
-        <v>629</v>
+        <v>405</v>
       </c>
       <c r="I3" t="n">
-        <v>284</v>
+        <v>148</v>
       </c>
       <c r="J3" t="n">
-        <v>39429830</v>
+        <v>9857253</v>
       </c>
       <c r="K3" t="n">
-        <v>43420489</v>
+        <v>10599609</v>
       </c>
       <c r="L3" t="n">
-        <v>49823335</v>
+        <v>12106237</v>
       </c>
       <c r="M3" t="n">
-        <v>59883159</v>
+        <v>14838699</v>
       </c>
       <c r="N3" t="n">
-        <v>63834949</v>
+        <v>15943090</v>
       </c>
       <c r="O3" t="n">
-        <v>61981718</v>
+        <v>15436862</v>
       </c>
       <c r="P3" t="n">
-        <v>63435168</v>
+        <v>15842026</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9405986070632935</v>
+        <v>0.8883860111236572</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8793397545814514</v>
+        <v>0.771577000617981</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8217676877975464</v>
+        <v>0.6798021793365479</v>
       </c>
       <c r="U3" t="n">
-        <v>0.554057240486145</v>
+        <v>0.3750098645687103</v>
       </c>
       <c r="V3" t="n">
-        <v>0.869486391544342</v>
+        <v>0.7544305324554443</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9057582020759583</v>
+        <v>0.8196393847465515</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>17857588</v>
+        <v>4226955</v>
       </c>
       <c r="Z3" t="n">
-        <v>1701428</v>
+        <v>634345</v>
       </c>
       <c r="AA3" t="n">
-        <v>74417</v>
+        <v>29509</v>
       </c>
       <c r="AB3" t="n">
-        <v>43535</v>
+        <v>14127</v>
       </c>
       <c r="AC3" t="n">
-        <v>1450</v>
+        <v>987</v>
       </c>
       <c r="AD3" t="n">
-        <v>251</v>
+        <v>101</v>
       </c>
       <c r="AE3" t="n">
-        <v>39430512</v>
+        <v>9857628</v>
       </c>
       <c r="AF3" t="n">
-        <v>42709567</v>
+        <v>10453593</v>
       </c>
       <c r="AG3" t="n">
-        <v>48978861</v>
+        <v>11942041</v>
       </c>
       <c r="AH3" t="n">
-        <v>59568174</v>
+        <v>14786674</v>
       </c>
       <c r="AI3" t="n">
-        <v>63744488</v>
+        <v>15923845</v>
       </c>
       <c r="AJ3" t="n">
-        <v>61829012</v>
+        <v>15406967</v>
       </c>
       <c r="AK3" t="n">
-        <v>63391622</v>
+        <v>15832657</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9074591398239136</v>
+        <v>0.8615846633911133</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.8068717122077942</v>
+        <v>0.7138553261756897</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.7283802628517151</v>
+        <v>0.6155587434768677</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.4818360507488251</v>
+        <v>0.3440484404563904</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.7934591174125671</v>
+        <v>0.6948884129524231</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.8487749695777893</v>
+        <v>0.7699460983276367</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.05065109303700365</v>
       </c>
       <c r="C4" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D4" t="n">
-        <v>1118303</v>
+        <v>536629</v>
       </c>
       <c r="E4" t="n">
-        <v>11320880</v>
+        <v>2492260</v>
       </c>
       <c r="F4" t="n">
-        <v>399686</v>
+        <v>180371</v>
       </c>
       <c r="G4" t="n">
-        <v>13567</v>
+        <v>6648</v>
       </c>
       <c r="H4" t="n">
-        <v>20116</v>
+        <v>12982</v>
       </c>
       <c r="I4" t="n">
-        <v>1674</v>
+        <v>1151</v>
       </c>
       <c r="J4" t="n">
-        <v>682</v>
+        <v>375</v>
       </c>
       <c r="K4" t="n">
-        <v>1182442</v>
+        <v>564767</v>
       </c>
       <c r="L4" t="n">
-        <v>1583969</v>
+        <v>734077</v>
       </c>
       <c r="M4" t="n">
-        <v>683711</v>
+        <v>301473</v>
       </c>
       <c r="N4" t="n">
-        <v>92323</v>
+        <v>38619</v>
       </c>
       <c r="O4" t="n">
-        <v>264585</v>
+        <v>124285</v>
       </c>
       <c r="P4" t="n">
-        <v>73240</v>
+        <v>35028</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999862909317017</v>
+        <v>0.9999697804450989</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9402760863304138</v>
+        <v>0.8868327140808105</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8782975673675537</v>
+        <v>0.7720250487327576</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8193826675415039</v>
+        <v>0.6784834861755371</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6106608510017395</v>
+        <v>0.414274126291275</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8697105050086975</v>
+        <v>0.7550027370452881</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9055398106575012</v>
+        <v>0.819308876991272</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1793382</v>
+        <v>674862</v>
       </c>
       <c r="Z4" t="n">
-        <v>10387905</v>
+        <v>2305814</v>
       </c>
       <c r="AA4" t="n">
-        <v>608586</v>
+        <v>212641</v>
       </c>
       <c r="AB4" t="n">
-        <v>39858</v>
+        <v>13807</v>
       </c>
       <c r="AC4" t="n">
-        <v>40802</v>
+        <v>20791</v>
       </c>
       <c r="AD4" t="n">
-        <v>3763</v>
+        <v>2171</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1893364</v>
+        <v>710783</v>
       </c>
       <c r="AG4" t="n">
-        <v>2428443</v>
+        <v>898273</v>
       </c>
       <c r="AH4" t="n">
-        <v>998696</v>
+        <v>353498</v>
       </c>
       <c r="AI4" t="n">
-        <v>182784</v>
+        <v>57864</v>
       </c>
       <c r="AJ4" t="n">
-        <v>417291</v>
+        <v>154180</v>
       </c>
       <c r="AK4" t="n">
-        <v>116786</v>
+        <v>44397</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9057955741882324</v>
+        <v>0.8588088154792786</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.808691680431366</v>
+        <v>0.71673983335495</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.7293912768363953</v>
+        <v>0.6169249415397644</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.4823915064334869</v>
+        <v>0.3446566164493561</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.7940601110458374</v>
+        <v>0.695707380771637</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.8488518595695496</v>
+        <v>0.7701113820075989</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="D5" t="n">
-        <v>37131</v>
+        <v>16872</v>
       </c>
       <c r="E5" t="n">
-        <v>429446</v>
+        <v>191495</v>
       </c>
       <c r="F5" t="n">
-        <v>3052645</v>
+        <v>632371</v>
       </c>
       <c r="G5" t="n">
-        <v>36767</v>
+        <v>14828</v>
       </c>
       <c r="H5" t="n">
-        <v>150187</v>
+        <v>69293</v>
       </c>
       <c r="I5" t="n">
-        <v>8463</v>
+        <v>5314</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1168940</v>
+        <v>547581</v>
       </c>
       <c r="L5" t="n">
-        <v>1553416</v>
+        <v>737826</v>
       </c>
       <c r="M5" t="n">
-        <v>662085</v>
+        <v>297857</v>
       </c>
       <c r="N5" t="n">
-        <v>158010</v>
+        <v>55431</v>
       </c>
       <c r="O5" t="n">
-        <v>265634</v>
+        <v>125057</v>
       </c>
       <c r="P5" t="n">
-        <v>72867</v>
+        <v>34872</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.99998939037323</v>
+        <v>0.9999766945838928</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9634206295013428</v>
+        <v>0.9307827949523926</v>
       </c>
       <c r="S5" t="n">
-        <v>0.95119309425354</v>
+        <v>0.908409059047699</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9790640473365784</v>
+        <v>0.9627059698104858</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9961056709289551</v>
+        <v>0.9941475987434387</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9917516112327576</v>
+        <v>0.9844843745231628</v>
       </c>
       <c r="W5" t="n">
-        <v>0.99772709608078</v>
+        <v>0.9956504106521606</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>59870</v>
+        <v>23010</v>
       </c>
       <c r="Z5" t="n">
-        <v>643769</v>
+        <v>226432</v>
       </c>
       <c r="AA5" t="n">
-        <v>2705736</v>
+        <v>572610</v>
       </c>
       <c r="AB5" t="n">
-        <v>55681</v>
+        <v>16757</v>
       </c>
       <c r="AC5" t="n">
-        <v>232966</v>
+        <v>83037</v>
       </c>
       <c r="AD5" t="n">
-        <v>16708</v>
+        <v>8382</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1821081</v>
+        <v>679069</v>
       </c>
       <c r="AG5" t="n">
-        <v>2486391</v>
+        <v>924272</v>
       </c>
       <c r="AH5" t="n">
-        <v>1008994</v>
+        <v>357618</v>
       </c>
       <c r="AI5" t="n">
-        <v>183600</v>
+        <v>58177</v>
       </c>
       <c r="AJ5" t="n">
-        <v>420372</v>
+        <v>155379</v>
       </c>
       <c r="AK5" t="n">
-        <v>116926</v>
+        <v>44480</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9422160387039185</v>
+        <v>0.9135147929191589</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9235421419143677</v>
+        <v>0.8865899443626404</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9687672853469849</v>
+        <v>0.9557499289512634</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9943003058433533</v>
+        <v>0.9927791953086853</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9869688749313354</v>
+        <v>0.9807373285293579</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9963642358779907</v>
+        <v>0.9944695234298706</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>237</v>
+        <v>126</v>
       </c>
       <c r="D6" t="n">
-        <v>26861</v>
+        <v>11187</v>
       </c>
       <c r="E6" t="n">
-        <v>32153</v>
+        <v>12735</v>
       </c>
       <c r="F6" t="n">
-        <v>68355</v>
+        <v>19332</v>
       </c>
       <c r="G6" t="n">
-        <v>196318</v>
+        <v>33260</v>
       </c>
       <c r="H6" t="n">
-        <v>27426</v>
+        <v>10649</v>
       </c>
       <c r="I6" t="n">
-        <v>2978</v>
+        <v>1402</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>39538</v>
+        <v>12528</v>
       </c>
       <c r="Z6" t="n">
-        <v>40699</v>
+        <v>14491</v>
       </c>
       <c r="AA6" t="n">
-        <v>60750</v>
+        <v>18090</v>
       </c>
       <c r="AB6" t="n">
-        <v>170728</v>
+        <v>30514</v>
       </c>
       <c r="AC6" t="n">
-        <v>38246</v>
+        <v>11381</v>
       </c>
       <c r="AD6" t="n">
-        <v>4367</v>
+        <v>1687</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>91</v>
+        <v>43</v>
       </c>
       <c r="D7" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="E7" t="n">
-        <v>18699</v>
+        <v>12645</v>
       </c>
       <c r="F7" t="n">
-        <v>157845</v>
+        <v>73921</v>
       </c>
       <c r="G7" t="n">
-        <v>29105</v>
+        <v>11397</v>
       </c>
       <c r="H7" t="n">
-        <v>1769663</v>
+        <v>384196</v>
       </c>
       <c r="I7" t="n">
-        <v>59841</v>
+        <v>27013</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>396</v>
+        <v>328</v>
       </c>
       <c r="Z7" t="n">
-        <v>40532</v>
+        <v>21886</v>
       </c>
       <c r="AA7" t="n">
-        <v>246662</v>
+        <v>89027</v>
       </c>
       <c r="AB7" t="n">
-        <v>41085</v>
+        <v>12082</v>
       </c>
       <c r="AC7" t="n">
-        <v>1614925</v>
+        <v>353874</v>
       </c>
       <c r="AD7" t="n">
-        <v>91697</v>
+        <v>32056</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="D8" t="n">
-        <v>94</v>
+        <v>41</v>
       </c>
       <c r="E8" t="n">
-        <v>946</v>
+        <v>597</v>
       </c>
       <c r="F8" t="n">
-        <v>4048</v>
+        <v>2509</v>
       </c>
       <c r="G8" t="n">
-        <v>1492</v>
+        <v>752</v>
       </c>
       <c r="H8" t="n">
-        <v>66227</v>
+        <v>30956</v>
       </c>
       <c r="I8" t="n">
-        <v>700325</v>
+        <v>158474</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>178</v>
+        <v>55</v>
       </c>
       <c r="Z8" t="n">
-        <v>2015</v>
+        <v>1119</v>
       </c>
       <c r="AA8" t="n">
-        <v>8281</v>
+        <v>4231</v>
       </c>
       <c r="AB8" t="n">
-        <v>2625</v>
+        <v>1091</v>
       </c>
       <c r="AC8" t="n">
-        <v>103827</v>
+        <v>37984</v>
       </c>
       <c r="AD8" t="n">
-        <v>656266</v>
+        <v>148866</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
